--- a/output/pdf_financials_xlsx/PSIL.xlsx
+++ b/output/pdf_financials_xlsx/PSIL.xlsx
@@ -1652,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.210287</v>
       </c>
     </row>
     <row r="93">
@@ -2560,7 +2560,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PSIL.xlsx
+++ b/output/pdf_financials_xlsx/PSIL.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.0009810000000000001</v>
+        <v>0.003981</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.001343</v>
+        <v>0.020644</v>
       </c>
     </row>
     <row r="8">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001696</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.016348</v>
       </c>
     </row>
     <row r="102">
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.043652</v>
+        <v>-0.045348</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.087051</v>
+        <v>0.070703</v>
       </c>
     </row>
     <row r="107">
@@ -2756,7 +2756,11 @@
           <t>GST receivables</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>-0.001696</v>
       </c>
@@ -2968,7 +2972,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.337364</v>
       </c>
@@ -3310,7 +3318,11 @@
           <t>Office expenses 8</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>0.003</v>
       </c>
